--- a/IW-GRUPO4-RETO7/TAREAS REALIZADAS PROYECTO COLABORATIVO.xlsx
+++ b/IW-GRUPO4-RETO7/TAREAS REALIZADAS PROYECTO COLABORATIVO.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Deusto\Desktop\INGENIERIA WEB 2026\PROYECTO COLABORATIVO\IW-GRUPO4-RETO7\IW-GRUPO4-RETO7\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Deusto\Desktop\Proyecto IW\IW-GRUPO4-RETO7\IW-GRUPO4-RETO7\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{51B2EA8E-ADF1-4412-AD3F-2265F1D8DADC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18CBFB64-DDD7-4D53-84E8-39347504D8F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{2CD3B6B2-1795-4DA6-96FE-5FE18B58DBC8}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{2CD3B6B2-1795-4DA6-96FE-5FE18B58DBC8}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="15">
   <si>
     <t>MIEMBRO</t>
   </si>
@@ -78,6 +78,12 @@
   </si>
   <si>
     <t>CSS (Base.html e Index.html)</t>
+  </si>
+  <si>
+    <t>Ekaitz</t>
+  </si>
+  <si>
+    <t>Lista usuarios html, menu crear usuarios html y todo lo de la clase de 4/5/2026 sobre Ngrok y Neon</t>
   </si>
 </sst>
 </file>
@@ -115,7 +121,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -138,17 +144,36 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -483,26 +508,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C07F5612-4219-4B33-AF6F-1B609EC35784}">
-  <dimension ref="A1:C10"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:C11"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.7265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="85.36328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.08984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="85.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.33203125" style="5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -513,7 +538,7 @@
         <v>46134</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
@@ -524,7 +549,7 @@
         <v>46134</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
@@ -535,7 +560,7 @@
         <v>46134</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
@@ -546,7 +571,7 @@
         <v>46134</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>3</v>
       </c>
@@ -557,7 +582,7 @@
         <v>46134</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>3</v>
       </c>
@@ -568,7 +593,7 @@
         <v>46134</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>3</v>
       </c>
@@ -579,7 +604,7 @@
         <v>46134</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>3</v>
       </c>
@@ -590,7 +615,7 @@
         <v>46134</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>3</v>
       </c>
@@ -599,6 +624,17 @@
       </c>
       <c r="C10" s="3">
         <v>46134</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11" s="7">
+        <v>46146</v>
       </c>
     </row>
   </sheetData>
@@ -607,6 +643,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x01010075ECDE16A1C43640B4EBAB3582408D3D" ma:contentTypeVersion="5" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="46dc5d1ec2b6311facbb370d8e25c627">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="e97e365b-4a29-4822-9b00-c21a01651a47" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="433a99258dba6a7cd95a3b02108bc2c1" ns3:_="">
     <xsd:import namespace="e97e365b-4a29-4822-9b00-c21a01651a47"/>
@@ -756,15 +801,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -774,6 +810,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{317EB5E7-FA69-47A1-BBEB-FA1A4CF4AE43}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{44A6DFFA-3DE9-40D4-9DDC-0356F2E000AC}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -791,14 +835,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{317EB5E7-FA69-47A1-BBEB-FA1A4CF4AE43}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E96EA4F0-4A01-46AF-BD46-805594251BD0}">
   <ds:schemaRefs>

--- a/IW-GRUPO4-RETO7/TAREAS REALIZADAS PROYECTO COLABORATIVO.xlsx
+++ b/IW-GRUPO4-RETO7/TAREAS REALIZADAS PROYECTO COLABORATIVO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Deusto\Desktop\Proyecto IW\IW-GRUPO4-RETO7\IW-GRUPO4-RETO7\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18CBFB64-DDD7-4D53-84E8-39347504D8F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D55A7817-A699-432C-8AC4-4830698D4874}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{2CD3B6B2-1795-4DA6-96FE-5FE18B58DBC8}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="16">
   <si>
     <t>MIEMBRO</t>
   </si>
@@ -84,6 +84,9 @@
   </si>
   <si>
     <t>Lista usuarios html, menu crear usuarios html y todo lo de la clase de 4/5/2026 sobre Ngrok y Neon</t>
+  </si>
+  <si>
+    <t>Acabar de crear, editar y eliminar usuarios, recursos y reservas</t>
   </si>
 </sst>
 </file>
@@ -161,7 +164,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -172,7 +175,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -508,7 +510,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C07F5612-4219-4B33-AF6F-1B609EC35784}">
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.77734375" bestFit="1" customWidth="1"/>
@@ -627,14 +629,25 @@
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" s="6" t="s">
+      <c r="A11" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C11" s="7">
+      <c r="C11" s="6">
         <v>46146</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C12" s="6">
+        <v>46147</v>
       </c>
     </row>
   </sheetData>
@@ -643,15 +656,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x01010075ECDE16A1C43640B4EBAB3582408D3D" ma:contentTypeVersion="5" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="46dc5d1ec2b6311facbb370d8e25c627">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="e97e365b-4a29-4822-9b00-c21a01651a47" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="433a99258dba6a7cd95a3b02108bc2c1" ns3:_="">
     <xsd:import namespace="e97e365b-4a29-4822-9b00-c21a01651a47"/>
@@ -801,6 +805,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -810,14 +823,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{317EB5E7-FA69-47A1-BBEB-FA1A4CF4AE43}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{44A6DFFA-3DE9-40D4-9DDC-0356F2E000AC}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -835,6 +840,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{317EB5E7-FA69-47A1-BBEB-FA1A4CF4AE43}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E96EA4F0-4A01-46AF-BD46-805594251BD0}">
   <ds:schemaRefs>

--- a/IW-GRUPO4-RETO7/TAREAS REALIZADAS PROYECTO COLABORATIVO.xlsx
+++ b/IW-GRUPO4-RETO7/TAREAS REALIZADAS PROYECTO COLABORATIVO.xlsx
@@ -1,113 +1,131 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Deusto\Desktop\Proyecto IW\IW-GRUPO4-RETO7\IW-GRUPO4-RETO7\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D55A7817-A699-432C-8AC4-4830698D4874}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="Calc"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{2CD3B6B2-1795-4DA6-96FE-5FE18B58DBC8}"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
+    <sheet name="Hoja1" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="2"/>
+    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
+      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="16">
-  <si>
-    <t>MIEMBRO</t>
-  </si>
-  <si>
-    <t>TAREA REALIZADA</t>
-  </si>
-  <si>
-    <t>FECHA</t>
-  </si>
-  <si>
-    <t>Oier</t>
-  </si>
-  <si>
-    <t>Proyecto y App</t>
-  </si>
-  <si>
-    <t>Estructura de carpetas</t>
-  </si>
-  <si>
-    <t>Base.html e index.hmtl</t>
-  </si>
-  <si>
-    <t>vistas (index, lista_usuarios, lista_recursos, lista_reservas, crear_usuario, crear_recurso, crear_reserva)</t>
-  </si>
-  <si>
-    <t>modelos (Usuario, Recurso, Reserva)</t>
-  </si>
-  <si>
-    <t>Formularios (UsuarioForm, RecursoForm, ReservaForm)</t>
-  </si>
-  <si>
-    <t>Imágenes ( logo-deusto.png, laboratorio.jpg, normas.jpg, objetivos.jpg)</t>
-  </si>
-  <si>
-    <t>Urls (index, lista_usuarios, lista_recursos, lista_reservas, crear_usuario, crear_recurso, crear_reserva)</t>
-  </si>
-  <si>
-    <t>CSS (Base.html e Index.html)</t>
-  </si>
-  <si>
-    <t>Ekaitz</t>
-  </si>
-  <si>
-    <t>Lista usuarios html, menu crear usuarios html y todo lo de la clase de 4/5/2026 sobre Ngrok y Neon</t>
-  </si>
-  <si>
-    <t>Acabar de crear, editar y eliminar usuarios, recursos y reservas</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="22">
+  <si>
+    <t xml:space="preserve">MIEMBRO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAREA REALIZADA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FECHA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Proyecto y App</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estructura de carpetas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Base.html e index.hmtl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">modelos (Usuario, Recurso, Reserva)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vistas (index, lista_usuarios, lista_recursos, lista_reservas, crear_usuario, crear_recurso, crear_reserva)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Formularios (UsuarioForm, RecursoForm, ReservaForm)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Imágenes ( logo-deusto.png, laboratorio.jpg, normas.jpg, objetivos.jpg)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CSS (Base.html e Index.html)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Urls (index, lista_usuarios, lista_recursos, lista_reservas, crear_usuario, crear_recurso, crear_reserva)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ekaitz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lista usuarios html, menu crear usuarios html y todo lo de la clase de 4/5/2026 sobre Ngrok y Neon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acabar de crear, editar y eliminar usuarios, recursos y reservas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Izaro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Uso de una rama ‘branch1’ para evitar solapamientos en el código</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leves cambios en el formato visual de fecha y hora</t>
+  </si>
+  <si>
+    <t xml:space="preserve">07/052026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ampliación: Regular conflictos horarios. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ampliación: Reserva de varios recursos para una misma actividad</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="General"/>
+    <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
+  </numFmts>
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
-      <scheme val="minor"/>
+      <charset val="1"/>
     </font>
     <font>
-      <b/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <b val="true"/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
-      <scheme val="minor"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -120,269 +138,191 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
+        <bgColor rgb="FFFFFF00"/>
       </patternFill>
     </fill>
   </fills>
   <borders count="3">
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  <cellStyleXfs count="20">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
   <cellXfs count="7">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="15" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
+    <cellStyle name="Currency" xfId="17" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
+    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tema de Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:srgbClr val="ffffff"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="0E2841"/>
+        <a:srgbClr val="0e2841"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E8E8E8"/>
+        <a:srgbClr val="e8e8e8"/>
       </a:lt2>
       <a:accent1>
         <a:srgbClr val="156082"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="E97132"/>
+        <a:srgbClr val="e97132"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="196B24"/>
+        <a:srgbClr val="196b24"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="0F9ED5"/>
+        <a:srgbClr val="0f9ed5"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="A02B93"/>
+        <a:srgbClr val="a02b93"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="4EA72E"/>
+        <a:srgbClr val="4ea72e"/>
       </a:accent6>
       <a:hlink>
         <a:srgbClr val="467886"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="96607D"/>
+        <a:srgbClr val="96607d"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204" pitchFamily="0" charset="1"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:latin typeface="Aptos Narrow" panose="02110004020202020204" pitchFamily="0" charset="1"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme>
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
                 <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
                 <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
                 <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
                 <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
                 <a:lumMod val="102000"/>
                 <a:tint val="94000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
                 <a:lumMod val="100000"/>
                 <a:shade val="100000"/>
               </a:schemeClr>
@@ -390,33 +330,24 @@
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
                 <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
         <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
@@ -429,13 +360,7 @@
           <a:effectLst/>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
+          <a:effectLst/>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
@@ -445,15 +370,13 @@
         <a:solidFill>
           <a:schemeClr val="phClr">
             <a:tint val="95000"/>
-            <a:satMod val="170000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="93000"/>
-                <a:satMod val="150000"/>
                 <a:shade val="98000"/>
                 <a:lumMod val="102000"/>
               </a:schemeClr>
@@ -461,7 +384,6 @@
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
                 <a:tint val="98000"/>
-                <a:satMod val="130000"/>
                 <a:shade val="90000"/>
                 <a:lumMod val="103000"/>
               </a:schemeClr>
@@ -469,189 +391,215 @@
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="63000"/>
-                <a:satMod val="120000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C07F5612-4219-4B33-AF6F-1B609EC35784}">
-  <dimension ref="A1:C12"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:C16"/>
+  <sheetFormatPr defaultColWidth="10.6015625" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="8.77734375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="85.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.33203125" style="5" bestFit="1" customWidth="1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8.78"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="85.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="10.33"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
+    <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="3">
+      <c r="C2" s="5" t="n">
         <v>46134</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
+    <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="3">
+      <c r="C3" s="5" t="n">
         <v>46134</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
+    <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="3">
+      <c r="C4" s="5" t="n">
         <v>46134</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
+    <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>46134</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="3">
+      <c r="C6" s="5" t="n">
         <v>46134</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
+    <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" s="3">
+      <c r="B7" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="5" t="n">
         <v>46134</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="s">
+    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="3">
+      <c r="B8" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="5" t="n">
         <v>46134</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" s="1" t="s">
+    <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C8" s="3">
+      <c r="B9" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9" s="5" t="n">
         <v>46134</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" s="1" t="s">
+    <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B10" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="3">
+      <c r="C10" s="5" t="n">
         <v>46134</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C10" s="3">
-        <v>46134</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" s="1" t="s">
+    <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="B11" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C11" s="6">
+      <c r="C11" s="6" t="n">
         <v>46146</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12" s="1" t="s">
+    <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B12" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C12" s="6">
+      <c r="C12" s="6" t="n">
         <v>46147</v>
       </c>
     </row>
+    <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="C13" s="1" t="n">
+        <v>46148</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="B14" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="B15" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="B16" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 

--- a/IW-GRUPO4-RETO7/TAREAS REALIZADAS PROYECTO COLABORATIVO.xlsx
+++ b/IW-GRUPO4-RETO7/TAREAS REALIZADAS PROYECTO COLABORATIVO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Deusto\Desktop\Proyecto IW\IW-GRUPO4-RETO7\IW-GRUPO4-RETO7\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D55A7817-A699-432C-8AC4-4830698D4874}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A17095E-B49A-4632-8FF4-1FA861B38BA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{2CD3B6B2-1795-4DA6-96FE-5FE18B58DBC8}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="21">
   <si>
     <t>MIEMBRO</t>
   </si>
@@ -87,6 +87,21 @@
   </si>
   <si>
     <t>Acabar de crear, editar y eliminar usuarios, recursos y reservas</t>
+  </si>
+  <si>
+    <t>Izaro</t>
+  </si>
+  <si>
+    <t>Uso de una rama ‘branch1’ para evitar solapamientos en el código</t>
+  </si>
+  <si>
+    <t>Leves cambios en el formato visual de fecha y hora</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ampliación: Regular conflictos horarios. </t>
+  </si>
+  <si>
+    <t>Ampliación: Reserva de varios recursos para una misma actividad</t>
   </si>
 </sst>
 </file>
@@ -510,7 +525,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C07F5612-4219-4B33-AF6F-1B609EC35784}">
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.77734375" bestFit="1" customWidth="1"/>
@@ -650,12 +665,66 @@
         <v>46147</v>
       </c>
     </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C13" s="3">
+        <v>46148</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14" s="3">
+        <v>46149</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C15" s="3">
+        <v>46149</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C16" s="3">
+        <v>46149</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x01010075ECDE16A1C43640B4EBAB3582408D3D" ma:contentTypeVersion="5" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="46dc5d1ec2b6311facbb370d8e25c627">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="e97e365b-4a29-4822-9b00-c21a01651a47" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="433a99258dba6a7cd95a3b02108bc2c1" ns3:_="">
     <xsd:import namespace="e97e365b-4a29-4822-9b00-c21a01651a47"/>
@@ -805,15 +874,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -823,6 +883,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{317EB5E7-FA69-47A1-BBEB-FA1A4CF4AE43}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{44A6DFFA-3DE9-40D4-9DDC-0356F2E000AC}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -840,14 +908,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{317EB5E7-FA69-47A1-BBEB-FA1A4CF4AE43}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E96EA4F0-4A01-46AF-BD46-805594251BD0}">
   <ds:schemaRefs>
